--- a/data/dataset_pirelli.xlsx
+++ b/data/dataset_pirelli.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAAE6041-B226-45FA-A2DE-1DD937915CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1499AE-50E5-49CC-B76C-0E9485A5A734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="222">
   <si>
     <t>id</t>
   </si>
@@ -602,15 +602,9 @@
     <t>sla</t>
   </si>
   <si>
-    <t>SLA 24 часа</t>
-  </si>
-  <si>
     <t>sla_30</t>
   </si>
   <si>
-    <t>SLA 30 часов</t>
-  </si>
-  <si>
     <t>sla_36</t>
   </si>
   <si>
@@ -693,6 +687,24 @@
   </si>
   <si>
     <t>rent_097</t>
+  </si>
+  <si>
+    <t>par</t>
+  </si>
+  <si>
+    <t>многокрит 24 часа</t>
+  </si>
+  <si>
+    <t>многокрит 30 часов</t>
+  </si>
+  <si>
+    <t>многокрит 36 часов</t>
+  </si>
+  <si>
+    <t>многокрит 42 часа</t>
+  </si>
+  <si>
+    <t>многокрит 48 часов</t>
   </si>
 </sst>
 </file>
@@ -14100,7 +14112,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C8A1A9-46B7-9940-8C25-AF214C0F8856}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -14160,7 +14172,7 @@
         <v>185</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="C3" s="15">
         <v>2</v>
@@ -14178,15 +14190,15 @@
         <v>1</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="C4" s="15">
         <v>3</v>
@@ -14204,15 +14216,15 @@
         <v>1</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -14230,15 +14242,15 @@
         <v>1</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="C6" s="15">
         <v>5</v>
@@ -14256,15 +14268,15 @@
         <v>1</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="C7" s="15">
         <v>6</v>
@@ -14282,15 +14294,15 @@
         <v>1</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="15" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C8" s="15">
         <v>7</v>
@@ -14299,7 +14311,7 @@
         <v>36</v>
       </c>
       <c r="E8" s="15">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="F8" s="15">
         <v>1</v>
@@ -14308,24 +14320,24 @@
         <v>1</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="15" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C9" s="15">
         <v>8</v>
       </c>
       <c r="D9" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E9" s="15">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="F9" s="15">
         <v>1</v>
@@ -14334,24 +14346,24 @@
         <v>1</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="15" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C10" s="15">
         <v>9</v>
       </c>
       <c r="D10" s="15">
-        <v>36</v>
-      </c>
-      <c r="E10" s="16">
-        <v>1.08</v>
+        <v>48</v>
+      </c>
+      <c r="E10" s="15">
+        <v>1</v>
       </c>
       <c r="F10" s="15">
         <v>1</v>
@@ -14360,15 +14372,15 @@
         <v>1</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="15" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C11" s="15">
         <v>10</v>
@@ -14376,8 +14388,8 @@
       <c r="D11" s="15">
         <v>36</v>
       </c>
-      <c r="E11" s="16">
-        <v>1.1200000000000001</v>
+      <c r="E11" s="15">
+        <v>0.88</v>
       </c>
       <c r="F11" s="15">
         <v>1</v>
@@ -14386,15 +14398,15 @@
         <v>1</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="15" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C12" s="15">
         <v>11</v>
@@ -14403,24 +14415,24 @@
         <v>36</v>
       </c>
       <c r="E12" s="15">
+        <v>0.92</v>
+      </c>
+      <c r="F12" s="15">
         <v>1</v>
-      </c>
-      <c r="F12" s="15">
-        <v>0.85</v>
       </c>
       <c r="G12" s="15">
         <v>1</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="15" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C13" s="15">
         <v>12</v>
@@ -14428,25 +14440,25 @@
       <c r="D13" s="15">
         <v>36</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="16">
+        <v>1.08</v>
+      </c>
+      <c r="F13" s="15">
         <v>1</v>
-      </c>
-      <c r="F13" s="15">
-        <v>0.91</v>
       </c>
       <c r="G13" s="15">
         <v>1</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="15" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C14" s="15">
         <v>13</v>
@@ -14454,25 +14466,25 @@
       <c r="D14" s="15">
         <v>36</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="16">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F14" s="15">
         <v>1</v>
-      </c>
-      <c r="F14" s="15">
-        <v>0.97</v>
       </c>
       <c r="G14" s="15">
         <v>1</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="15" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C15" s="15">
         <v>14</v>
@@ -14483,14 +14495,14 @@
       <c r="E15" s="15">
         <v>1</v>
       </c>
-      <c r="F15" s="16">
-        <v>1.03</v>
+      <c r="F15" s="15">
+        <v>0.85</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -14498,7 +14510,7 @@
         <v>214</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C16" s="15">
         <v>15</v>
@@ -14509,14 +14521,14 @@
       <c r="E16" s="15">
         <v>1</v>
       </c>
-      <c r="F16" s="16">
-        <v>1.0900000000000001</v>
+      <c r="F16" s="15">
+        <v>0.91</v>
       </c>
       <c r="G16" s="15">
         <v>1</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -14524,7 +14536,7 @@
         <v>215</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C17" s="15">
         <v>16</v>
@@ -14535,14 +14547,92 @@
       <c r="E17" s="15">
         <v>1</v>
       </c>
-      <c r="F17" s="16">
-        <v>1.1499999999999999</v>
+      <c r="F17" s="15">
+        <v>0.97</v>
       </c>
       <c r="G17" s="15">
         <v>1</v>
       </c>
       <c r="H17" s="15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="15" t="s">
         <v>211</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="15">
+        <v>17</v>
+      </c>
+      <c r="D18" s="15">
+        <v>36</v>
+      </c>
+      <c r="E18" s="15">
+        <v>1</v>
+      </c>
+      <c r="F18" s="16">
+        <v>1.03</v>
+      </c>
+      <c r="G18" s="15">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="15">
+        <v>18</v>
+      </c>
+      <c r="D19" s="15">
+        <v>36</v>
+      </c>
+      <c r="E19" s="15">
+        <v>1</v>
+      </c>
+      <c r="F19" s="16">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="G19" s="15">
+        <v>1</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="15">
+        <v>19</v>
+      </c>
+      <c r="D20" s="15">
+        <v>36</v>
+      </c>
+      <c r="E20" s="15">
+        <v>1</v>
+      </c>
+      <c r="F20" s="16">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G20" s="15">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/data/dataset_pirelli.xlsx
+++ b/data/dataset_pirelli.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1499AE-50E5-49CC-B76C-0E9485A5A734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF0278E-AF4E-4BB3-9E09-53208FF790D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="225">
   <si>
     <t>id</t>
   </si>
@@ -602,18 +602,12 @@
     <t>sla</t>
   </si>
   <si>
-    <t>sla_30</t>
-  </si>
-  <si>
     <t>sla_36</t>
   </si>
   <si>
     <t>SLA 36 часов</t>
   </si>
   <si>
-    <t>sla_42</t>
-  </si>
-  <si>
     <t>SLA 42 часа</t>
   </si>
   <si>
@@ -705,6 +699,21 @@
   </si>
   <si>
     <t>многокрит 48 часов</t>
+  </si>
+  <si>
+    <t>par_24</t>
+  </si>
+  <si>
+    <t>par_30</t>
+  </si>
+  <si>
+    <t>par_36</t>
+  </si>
+  <si>
+    <t>par_42</t>
+  </si>
+  <si>
+    <t>par_48</t>
   </si>
 </sst>
 </file>
@@ -14169,10 +14178,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="15" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C3" s="15">
         <v>2</v>
@@ -14190,15 +14199,15 @@
         <v>1</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="15" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C4" s="15">
         <v>3</v>
@@ -14216,15 +14225,15 @@
         <v>1</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="15" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C5" s="15">
         <v>4</v>
@@ -14242,15 +14251,15 @@
         <v>1</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="15" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C6" s="15">
         <v>5</v>
@@ -14268,15 +14277,15 @@
         <v>1</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="15" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C7" s="15">
         <v>6</v>
@@ -14294,7 +14303,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -14320,12 +14329,12 @@
         <v>1</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>186</v>
@@ -14346,12 +14355,12 @@
         <v>1</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>186</v>
@@ -14372,15 +14381,15 @@
         <v>1</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C11" s="15">
         <v>10</v>
@@ -14398,15 +14407,15 @@
         <v>1</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C12" s="15">
         <v>11</v>
@@ -14424,15 +14433,15 @@
         <v>1</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C13" s="15">
         <v>12</v>
@@ -14450,15 +14459,15 @@
         <v>1</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="15" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C14" s="15">
         <v>13</v>
@@ -14476,15 +14485,15 @@
         <v>1</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C15" s="15">
         <v>14</v>
@@ -14502,15 +14511,15 @@
         <v>1</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="15" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C16" s="15">
         <v>15</v>
@@ -14528,15 +14537,15 @@
         <v>1</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C17" s="15">
         <v>16</v>
@@ -14554,15 +14563,15 @@
         <v>1</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C18" s="15">
         <v>17</v>
@@ -14580,15 +14589,15 @@
         <v>1</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C19" s="15">
         <v>18</v>
@@ -14606,15 +14615,15 @@
         <v>1</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C20" s="15">
         <v>19</v>
@@ -14632,7 +14641,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/data/dataset_pirelli.xlsx
+++ b/data/dataset_pirelli.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF0278E-AF4E-4BB3-9E09-53208FF790D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB0B6BE-0760-465B-BCB8-3E0B3A9DE8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14317,7 +14317,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="15">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E8" s="15">
         <v>1</v>
@@ -14343,7 +14343,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="15">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" s="15">
         <v>1</v>

--- a/data/dataset_pirelli.xlsx
+++ b/data/dataset_pirelli.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\polin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB0B6BE-0760-465B-BCB8-3E0B3A9DE8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6328BC62-8306-4D10-AD47-39A47FA92CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
